--- a/benchmark-visuels/2026-10-24_benchmark-visuels-videos.xlsx
+++ b/benchmark-visuels/2026-10-24_benchmark-visuels-videos.xlsx
@@ -23593,7 +23593,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12 dernières publications par page, 10 pages B2B</t>
+          <t>12 dernières publications par page, 10 pages B2B (118 publications ; la page Payfit, surtout en espagnol, est écartée)</t>
         </is>
       </c>
     </row>
